--- a/data/trans_bre/P1803_2016_2023-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1803_2016_2023-Provincia-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,05</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 8,54</t>
+          <t>-0,82; 9,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 13,13</t>
+          <t>1,42; 11,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 153,28</t>
+          <t>-11,15; 166,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 118,74</t>
+          <t>7,6; 107,72</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,55</t>
+          <t>-1,62; 2,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 5,77</t>
+          <t>-1,31; 5,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,26; 215,27</t>
+          <t>-49,3; 262,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 152,88</t>
+          <t>-18,52; 137,71</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,67</t>
+          <t>-1,42; 2,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 6,15</t>
+          <t>-3,1; 5,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-67,49; 417,32</t>
+          <t>-64,25; 517,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 75,71</t>
+          <t>-23,17; 66,88</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-1,82</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-16,65%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,24</t>
+          <t>-4,82; 2,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 3,19</t>
+          <t>-2,73; 5,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,66; 61,37</t>
+          <t>-49,38; 53,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,65; 37,56</t>
+          <t>-21,77; 83,25</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-1,16</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-28,32%</t>
+          <t>-22,61%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,85</t>
+          <t>-1,34; 5,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 1,44</t>
+          <t>-4,44; 2,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-52,95; 533,67</t>
+          <t>-57,39; 591,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-75,88; 72,38</t>
+          <t>-71,4; 130,68</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 0,97</t>
+          <t>-7,63; 0,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 9,47</t>
+          <t>0,89; 9,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,16; 28,37</t>
+          <t>-74,75; 18,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 151,54</t>
+          <t>6,41; 167,33</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-11,44%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,1</t>
+          <t>-2,26; 3,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 3,54</t>
+          <t>-2,17; 5,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 80,74</t>
+          <t>-36,47; 79,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-58,54; 30,03</t>
+          <t>-13,78; 50,36</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-25,68</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-91,67%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,37</t>
+          <t>0,33; 5,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,25; 0,58</t>
+          <t>-1,36; 1,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,32; 176,18</t>
+          <t>3,98; 183,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-97,47; 30,79</t>
+          <t>-43,22; 105,76</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-5,42</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-36,46%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,94</t>
+          <t>-0,03; 2,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 1,69</t>
+          <t>0,52; 3,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 48,36</t>
+          <t>-0,54; 53,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-73,5; 19,99</t>
+          <t>5,72; 45,67</t>
         </is>
       </c>
     </row>
